--- a/JupyterNotebooks/delete.xlsx
+++ b/JupyterNotebooks/delete.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,281 +413,2686 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>default_order</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Categorization</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Word</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CAT_ORDER</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>State represents the current condition of an entity at a specific point in time. It answers the question “Where is this entity right now?” and reflects the most recent observed values of relevant measures, frequency, balances, etc. State is essential for anchoring decisions in the present but is insufficient on its own without historical context. In modeling, State provides immediacy and scale but must be interpreted alongside other dimensions to avoid over-reacting to short-term fluctuations. Examples Include: Current Deposit Balance, Current Month POS TXN Count, Number of Active Accounts.</t>
-        </is>
+      <c r="A2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B2" t="n">
+        <v>87</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Descriptive</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Descriptive represents summarized or smoothed representations of an entity’s behavior over a defined historical window. It answers the question “What does this entity typically look like?” by reducing short-term noise and highlighting central tendency or typical patterns across time. Descriptive measures provide stability and interpretability by contextualizing current behavior within a broader historical baseline. In modeling, Descriptive variables help prevent over-reaction to transient spikes or dips but must be carefully managed to avoid redundancy with State measures. Examples include Avg Balances, Maximums over an extended period of time.</t>
-        </is>
+      <c r="A3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B3" t="n">
+        <v>73</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Anchoring Effect</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A cognitive bias where people rely too heavily on the first piece of information (the “anchor”) when making decisions. Once an anchor is set, it influences subsequent judgments, even if it’s arbitrary or unrelated. For example, when asked whether the Eiffel Tower is taller or shorter than 500 feet, people’s estimates will cluster around that number. This bias can affect pricing, negotiations, and even forecasting.</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Diagnostic</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Diagnostic represents measures of directionality, momentum, or variability in an entity’s behavior over time. It answers the question “How is this entity changing?” by capturing growth, decline, volatility, or acceleration relative to prior periods. Diagnostic measures are essential for understanding trajectory, early warning signals, and emerging shifts that may not yet be visible in current state alone. In modeling, Diagnostic variables enhance interpretability and foresight but should be used cautiously, as excessive reliance can introduce instability and reduce cluster persistence. Diagnostic can be broken into 4 Categories, Trend, Momentum, Change and Volatility.</t>
-        </is>
+      <c r="A4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B4" t="n">
+        <v>74</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Base Rate Fallacy</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>People ignore or undervalue general statistical information (the base rate) and focus instead on specific information, often leading to incorrect conclusions. In decision-making, individuals may give more weight to anecdotal or vivid information, despite the broader statistical reality that should influence their judgment. Imagine a test for a rare disease that is 95% accurate. The disease affects 1 in 10,000 people. If a person tests positive, many might assume the likelihood of them having the disease is high. However, considering the base rate (the rarity of the disease), the probability of actually having the disease is still very low. In this scenario, the base rate fallacy would be ignoring the low prevalence of the disease (the base rate) and overestimating the accuracy of the test result, leading to an exaggerated belief in the likelihood of the person having the disease. The fallacy demonstrates how people's intuitive reasoning often neglects the significance of background statistical data in favor of more attention-grabbing or salient information.</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Structural</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Structural represents relatively stable attributes that describe how an entity is configured within the system rather than how it behaves at a given moment. It answers the question “What is the entity’s structural position?” by reflecting enduring characteristics such as product holdings, account composition, or long-term balances. Structural measures anchor and constrain behavior by defining capacity, access, and configuration. In modeling, Structural variables provide important context but should be included sparingly to avoid overwhelming activity-based signals or unintentionally clustering entities by size rather than behavior. Product Count, Product Flags, Tenure.</t>
-        </is>
+      <c r="A5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bureaucratic Politics</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Organization decision making paradigm in which decisions are made based solely on who is making the decision, specifically, they will decide in their own best interests. Counters prevalent theory in which a rational, fair or logical decision making process will occur.</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Contextual</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Contextual represents external or situational factors that influence behavior but are not behaviors themselves. It answers the question “What conditions surround this entity?” by capturing environmental, geographic, policy, or situational elements that shape observed actions. Contextual measures help explain why similar entities may behave differently under different circumstances. In modeling, Contextual variables are generally inappropriate as primary drivers of similarity but are critical for interpretation, validation, and responsible application of results. Examples include, Regional Indicator, Interest Rate Macro Flags, Employement Type)</t>
-        </is>
+      <c r="A6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B6" t="n">
+        <v>76</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Biased Assimilation</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tendency to interpret information in a way that supports a desired conclusion. </t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Demographic</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Demographic represents intrinsic attributes of an entity that change infrequently and describe who the entity is rather than what it does. It answers the question “Who is this entity?” by capturing characteristics such as age, household composition, or other identity-level descriptors. Demographic measures provide essential interpretive context and support equity-aware analysis but do not directly represent behavior. In modeling, Demographic variables are typically excluded from defining similarity to avoid embedding bias or non-actionable distinctions, and are instead used for post-hoc analysis, monitoring, and policy alignment. Examples inlcude, Member Age Band, Language Preferences, Postal Code, Household Parameters, etc.</t>
-        </is>
+      <c r="A7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B7" t="n">
+        <v>77</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Blind spot bias</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cognitive bias where people are unaware of their own biases, while easily recognizing the biases in others.  People tend to believe they are more objective, rational, and less susceptible to biases than others, even though they may exhibit the same biases in their own thinking. Self-awareness gap: People can easily identify cognitive biases (like confirmation bias, motivated reasoning, or stereotyping) in others, but fail to recognize these biases in themselves. Overconfidence in objectivity: Individuals often overestimate their own ability to reason without bias, which can lead to an inflated sense of confidence in their decisions and beliefs. Resistance to feedback: Blind spot bias can make people resistant to feedback, because they believe that they’re viewing situations or information more objectively than they actually are.</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Constraint represents limitations or enabling conditions that bound an entity’s range of possible behavior. It answers the question “What limits or enables this entity’s choices?” by approximating capacity, dependency, or stress through proxy measures such as income concentration or balance volatility. Constraint measures help distinguish inability from preference. In modeling, Constraint variables are best used diagnostically to interpret cluster composition rather than to define cluster membership.</t>
-        </is>
+      <c r="A8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Also known as Selective Perception. What people see can be strongly shaped by what they believe, using the example of a study which occurred during a especially dirty Princeton Dartmouth Football game. After the game people were asked to comment which team was "Dirtier" and results were based on which team individuals had allegiance with.
+Tendency to search for, interpret, and remember information in a way that confirms one’s preexisting beliefs or hypotheses. People often ignore or downplay evidence that contradicts their views. This bias can reinforce stereotypes, polarize opinions, and skew data interpretation. It’s especially important to watch for in research, media consumption, and decision-making.</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Constraint: Capacity</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Constraints which represent the fundamental economic or operational limits that bound an entity’s feasible range of actions, regardless of intent or preference. They are critical for distinguishing observed behavior from what is realistically possible, helping avoid misinterpretation of low activity as disinterest rather than limitation. In modeling, capacity constraints provide guardrails for ethical interpretation and prevent over-attribution of agency where structural limits exist. They are best used diagnostically to contextualize clusters and inform suitability, risk, and support decisions.
-Examples; Debt service ratio (estimated obligations ÷ inflows), Credit utilization rate, Liquidity coverage ratio (liquid balances ÷ monthly outflows)</t>
-        </is>
+      <c r="A9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fast statistics </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Immoderate, intuitive, visceral, and powerful.</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Constraint: Stability &amp; Fragility</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Constraints which capture the reliability and predictability of an entity’s financial or behavioral foundation rather than its current level or direction. They are important because volatility, dependency, or irregularity can severely limit planning ability and resilience even when averages appear healthy. These constraints help explain why entities with similar states behave differently under stress or change. In modeling, they support early risk identification and responsible interpretation without driving cluster formation.
-Examples; Balance volatility index, Income concentration ratio, Irregular inflow variability score</t>
-        </is>
+      <c r="A10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Slow statistics</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Thoughtful gathering of unbiased information.</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Constraint: Access &amp; Configuration</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Constraints which reflect limitations imposed by system setup, product availability, or channel enablement rather than by the entity’s choices. They are important because behavior cannot be meaningfully interpreted without understanding what options are actually available. These constraints help distinguish exclusion or friction from deliberate disengagement. In modeling, they ensure clusters are interpreted in light of opportunity sets rather than assumed preferences.
-Examples; Lack of revolving credit access flag, Digital banking enablement indicator, Funds locked in restricted or term products ratio</t>
-        </is>
+      <c r="A11" t="n">
+        <v>81</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Truth-default theory </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>54% accurate identifying liar. We can identify truth tellers far more easily, bad at identifying liars. We start in a default position of believing people and only when substantial evidence to the contrary presents itself do we change our position. In fact, we can even trivialize information away that in hindsight it rather pertinent. In a social experiment, teacher leaves room, answers are available, rando we've never met encouraging us to cheat.</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Constraint: Stress &amp; Load</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Constraints which represent sustained pressure that restricts flexibility and increases vulnerability, even if short-term indicators appear stable. They are important for identifying entities operating near or beyond their functional limits, where small shocks can lead to outsized effects. These constraints help explain brittle or reactive behaviors that are not captured by state alone. In modeling, they support responsible application by highlighting latent risk without over-weighting transient fluctuations.
-Examples: Frequency of negative net cash-flow periods, Overdraft reliance rate, Minimum balance breach frequency</t>
-        </is>
+      <c r="A12" t="n">
+        <v>82</v>
+      </c>
+      <c r="B12" t="n">
+        <v>82</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Illusion of Asymmetric Insights</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Belief that we know others better than they know us and that we may have insights about them that they lack (but not vice versa). As explained by the fill in the blanks word game, the words don't define me, yet they do define others. CIA Officers. Judges. </t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Constraint: Time &amp; Commitment</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Constraints which capture obligations that reduce an entity’s degrees of freedom over a defined horizon, independent of current behavior. They are important because long-term commitments can materially limit adaptability, even when present conditions seem favorable. These constraints help explain inertia, delayed responses, or resistance to change in observed behavior. In modeling, they provide critical context for interpreting persistence and transition dynamics across clusters. 
-Examples. Fixed commitment load (recurring debits ÷ outflows), Long-term product commitment score, Contractual tenure-weighted obligation index</t>
-        </is>
+      <c r="A13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Intertemporal choice</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Refers to decisions that involve trade-offs between costs and benefits occurring at different points in time</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Diagnostic - Change</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Measures the difference in a value between two defined points in time. It answers the question “How much did this metric increase or decrease?” by comparing a current period to a prior baseline. Change captures short-term movement and is often the first signal of emerging behavior. In modeling, Change variables are useful for detecting early shifts but can be noisy if used without context.
-Examples: Month-over-month change in total deposits, Change in transaction count compared to last month, Increase or decrease in average account balance since prior period</t>
-        </is>
+      <c r="A14" t="n">
+        <v>84</v>
+      </c>
+      <c r="B14" t="n">
+        <v>84</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Motivated reasoning</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Cognitive phenomenon where people process information in a biased way to support their existing beliefs, desires, or emotions. Instead of evaluating evidence objectively, individuals interpret information in a way that aligns with their preferred conclusions or outcomes. Directional reasoning: When people want to arrive at a specific conclusion, they give more weight to evidence that supports their desired belief and discount or dismiss evidence that contradicts it. Accuracy reasoning: In contrast, this occurs when individuals are genuinely motivated to arrive at a correct or objective conclusion. They carefully analyze all available evidence regardless of whether it supports their initial belief. 
+Type of cognitive bias where people process information in a way that aligns with their preexisting beliefs, desires, or emotions, rather than objectively evaluating the facts</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Diagnostic - Trend</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Describes the overall direction and pattern of change across multiple time periods rather than a single comparison. It answers “Is this behavior generally increasing, decreasing, or stable over time?” by smoothing short-term fluctuations. Trends provide insight into sustained behavioral movement and are more stable than point-in-time changes. In modeling, Trend variables help distinguish temporary spikes from meaningful trajectories.
-Examples: 6-month rolling trend in payroll deposits, Slope of average monthly balance over the past year, Directional trend in debit transaction volume</t>
-        </is>
+      <c r="A15" t="n">
+        <v>85</v>
+      </c>
+      <c r="B15" t="n">
+        <v>85</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Naive realism</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Naïve realism is a concept from social psychology and philosophy that describes the human tendency to believe that we see the world objectively, and that other people who disagree must be uninformed, irrational, or biased.  
+Naïve realism explains why disagreements can become hostile. We assume others are irrational or malicious instead of recognizing legitimate differences in perspective or interpretation. It makes it harder to understand or appreciate others’ viewpoints, since we believe our view is the only valid one.It contributes to us-vs-them mentalities in politics and culture. Each side thinks it's simply seeing "facts," while the other is deluded.In workplaces or teams, naïve realism can block constructive dialogue and creative problem-solving by dismissing dissenting ideas too quickly.</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Diagnostic - Volatility</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Measures how variable or inconsistent a metric is over time. It answers “How stable is this behavior?” by capturing dispersion, fluctuation, or unpredictability around a typical value. High volatility often indicates irregular engagement or financial instability, while low volatility suggests consistent behavior. In modeling, Volatility variables can be strong predictors but must be interpreted carefully to avoid overreacting to noise.
-Examples: Standard deviation of monthly deposits over 6 months, Variability in transaction counts across recent periods, Fluctuation in balance levels month to month</t>
-        </is>
+      <c r="A16" t="n">
+        <v>86</v>
+      </c>
+      <c r="B16" t="n">
+        <v>86</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ostrich Effect</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>cognitive bias where people avoid information they perceive as potentially unpleasant or negative—like an ostrich metaphorically "burying its head in the sand" to avoid danger (even though real ostriches don't actually do this).</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Diagnostic - Momentum</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Measures the rate and acceleration of change rather than the direction alone. It answers “Is this behavior changing faster or slowing down?” by assessing whether growth or decline is intensifying. Momentum highlights inflection points that may not yet be visible in overall trend. In modeling, Momentum variables are powerful early-warning indicators but can introduce instability if overused. It is effectively the second derivative, so the change of the change.
-Examples;  Acceleration in deposit growth over consecutive months, Increasing rate of decline in account balances, Speed of increase in digital transaction adoption</t>
-        </is>
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>What Meaning Does a KPI actually have?</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Before we figure out whether nurses have had a pay raise, first find out what is meant by “nurse.” 
+Before lamenting the prevalence of self-harm in young people, stop to consider whether you know what “self-harm” is supposed to mean. Before concluding that inequality has soared, ask, “Inequality of what?” Demanding a short, sharp answer to the question “Has inequality risen?” is not only unfair, but strangely incurious. If we are curious instead, and ask the right questions, deeper insight is within easy reach.
+Net Wealth not indicative of poverty, Doctor who just finished med school with $100k in debt.
+The billion poorest people who have a net worth of Zero might be poorer than someone with $5 as $0 doesn't add up fast.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Functional Role</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Describes how a variable is used within a specific model or modeling process, rather than what it represents conceptually. It classifies variables based on whether they actively shape the model (core), help interpret results (descriptive), or evaluate model quality and stability (diagnostic). For example, POS Transaction 6-Month Average may be a core variable that defines clusters, while Assignment Margin is diagnostic because it evaluates how confidently members are assigned. Classifying functional role is critical in ML modeling—especially in unsupervised learning—because it makes modeling assumptions explicit, prevents unintended variables from shaping outcomes, and enables controlled, explainable model evolution.</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Organizations</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Great at solving Problems. Bad at diagnosing problems. 
+You should never trust large organizations, on the best day they’re incompetent, on a bad day they’re crooked.</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Core Variables</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Primary drivers of similarity and distance in cluster formation. They directly define the behavioral dimensions the segmentation is intended to capture, and removing them would materially change cluster structure or archetype meaning. Core variables are included in distance calculations and must remain stable across model iterations to preserve interpretability. Core variables are most often State or Descriptive behavioral measures, and should be limited in number.</t>
-        </is>
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Think about the Medium</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Weekly, daily, hourly—the metronome of the news clock changes the very nature of what is news. Daily news always seems more informative than rolling news; weekly news is typically more informative than daily news.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Supporting</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Contribute to cluster separation, stability, or boundary refinement but do not independently define cluster identity. They may influence distance calculations or be used in secondary weighting, but clusters should remain interpretable without them. Supporting variables help smooth transitions, reduce ambiguity, or capture secondary behavior patterns. Supporting variables can include State, Descriptive, Structural, or Diagnostic measures.</t>
-        </is>
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Unintended Consequences KPIs</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Must consider what adverse effects one might create when measuring. Doctors won't operate on sick patients. Data needs to be understood. Maximum day wait for appointment, doctors stopped taking appointments.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Explanatory</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Not used in cluster formation or distance calculations. They provide interpretive context after clusters are formed, helping explain why clusters look the way they do rather than how they were created. These variables are often used for labeling, storytelling, validation, or governance review. Explanatory variables commonly include Structural, Contextual, or Demographic attributes.</t>
-        </is>
+      <c r="A21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Facts Vs Statistics</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>More likely to die in accident in evening than in morning. More drivers in evening than in morning.
+More likely to die in clear weather than fog. More time occurs without fog, what does it actually mean???
+9:1000 vs 16:1000 deaths in Navy vs NY. Who is in Navy, young healthy men, vs everyone else.
+Polio record cases 1952, more babies, financial incentives, changes on reporting standards, etc..
+Population in rural China, 28M than 5 years later 108M. Survey 1 was related to Military conscription, Survey 2 famine and relief</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Fact Believability</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Facts about this epidemic that have lasted a few days are far more reliable than the latest ‘facts’ that have just come out, which may be erroneous or unrepresentative and thus misleading . . . a question that today can be answered [by] only informed belief may perhaps be answered with a fact tomorrow.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>94</v>
+      </c>
+      <c r="B23" t="n">
+        <v>94</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>63</v>
+      </c>
+      <c r="B24" t="n">
+        <v>63</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FINALNAME</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>65</v>
+      </c>
+      <c r="B26" t="n">
+        <v>65</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>METRIC_TYPE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>66</v>
+      </c>
+      <c r="B27" t="n">
+        <v>66</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>METRIC_CLASSIFICATION</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>67</v>
+      </c>
+      <c r="B28" t="n">
+        <v>67</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PRODUCT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>68</v>
+      </c>
+      <c r="B29" t="n">
+        <v>68</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>69</v>
+      </c>
+      <c r="B30" t="n">
+        <v>69</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>METRIC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>70</v>
+      </c>
+      <c r="B31" t="n">
+        <v>70</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>71</v>
+      </c>
+      <c r="B32" t="n">
+        <v>71</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RECORD_TYPE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>72</v>
+      </c>
+      <c r="B33" t="n">
+        <v>72</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Data Dictionary</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Data Dictionary Columns</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>UPDATE_DATE</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>90</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Objects Categorization</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Objects Categorization</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Relative Order</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>13</v>
+      </c>
+      <c r="B37" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Objects Categorization</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Column List</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>14</v>
+      </c>
+      <c r="B38" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Objects Categorization</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Material Change Log</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>15</v>
+      </c>
+      <c r="B39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Objects Categorization</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>16</v>
+      </c>
+      <c r="B40" t="n">
+        <v>16</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Objects Categorization</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Reference String</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B41" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Objects Categorization</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Reference Dictionary</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>88</v>
+      </c>
+      <c r="B42" t="n">
+        <v>88</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>93</v>
+      </c>
+      <c r="B46" t="n">
+        <v>93</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>47</v>
+      </c>
+      <c r="B47" t="n">
+        <v>47</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Process/ Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" t="n">
+        <v>48</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>49</v>
+      </c>
+      <c r="B49" t="n">
+        <v>49</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
+Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B50" t="n">
+        <v>50</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
+Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
+Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>51</v>
+      </c>
+      <c r="B51" t="n">
+        <v>51</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Exploratory Data Analysis</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
+While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="n">
+        <v>52</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>53</v>
+      </c>
+      <c r="B53" t="n">
+        <v>53</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
+It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>54</v>
+      </c>
+      <c r="B54" t="n">
+        <v>54</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>55</v>
+      </c>
+      <c r="B55" t="n">
+        <v>55</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>58</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>59</v>
+      </c>
+      <c r="B59" t="n">
+        <v>59</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>60</v>
+      </c>
+      <c r="B60" t="n">
+        <v>60</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>61</v>
+      </c>
+      <c r="B61" t="n">
+        <v>61</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Variables used to track outcomes, drift, or post-engagement effects over time. Monitoring variables are excluded from clustering inputs to avoid leakage but are essential for evaluating stability and impact.</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B62" t="n">
+        <v>62</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Machine Learning Framework</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>91</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>18</v>
+      </c>
+      <c r="B64" t="n">
+        <v>18</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>19</v>
+      </c>
+      <c r="B65" t="n">
+        <v>19</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20</v>
+      </c>
+      <c r="B66" t="n">
+        <v>20</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Guiding Principle</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>21</v>
+      </c>
+      <c r="B67" t="n">
+        <v>21</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>22</v>
+      </c>
+      <c r="B68" t="n">
+        <v>22</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>23</v>
+      </c>
+      <c r="B69" t="n">
+        <v>23</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>24</v>
+      </c>
+      <c r="B70" t="n">
+        <v>24</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Expected Outcomes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>25</v>
+      </c>
+      <c r="B71" t="n">
+        <v>25</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
+Ultimately it is the questions, How do we compute it.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>26</v>
+      </c>
+      <c r="B72" t="n">
+        <v>26</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Algorithm</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>27</v>
+      </c>
+      <c r="B73" t="n">
+        <v>27</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Categorization Filter Order</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>89</v>
+      </c>
+      <c r="B74" t="n">
+        <v>89</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Organization - Definition</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Organization - Definition</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>7</v>
+      </c>
+      <c r="B75" t="n">
+        <v>7</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Organization - Definition</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>What is it.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>This google sheet is my primary source to store element level definitions, including attributes and element level information. This is the master data source for all individual definitions.</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>8</v>
+      </c>
+      <c r="B76" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Organization - Definition</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>The definition of Process as it relates to this sheet is more complex, specifically Words can be associated with a Process, even though it is not tagged by a process.
+Example: Anchoring Effect - Process: Behavioural Economics, Classification: Definition
+Example: Model Evaluation - Process: General Definition, Classification: Definition
+Anchoring Effect specifically relates to a explicit discpline, and there is value in being able to filter it as a Behavioural Economics classification. Where as Model Evaluation, is general it relates to a number of processes, and should be included in them directly. As a default, using General Definition/ Definition is the safest option.</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>92</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>28</v>
+      </c>
+      <c r="B78" t="n">
+        <v>28</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Process/ Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>29</v>
+      </c>
+      <c r="B79" t="n">
+        <v>29</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>30</v>
+      </c>
+      <c r="B80" t="n">
+        <v>30</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>31</v>
+      </c>
+      <c r="B81" t="n">
+        <v>31</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
+Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>32</v>
+      </c>
+      <c r="B82" t="n">
+        <v>32</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Root Cause Analysis</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>33</v>
+      </c>
+      <c r="B83" t="n">
+        <v>33</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Research and Exploration</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>34</v>
+      </c>
+      <c r="B84" t="n">
+        <v>34</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>35</v>
+      </c>
+      <c r="B85" t="n">
+        <v>35</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Solution Design</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>36</v>
+      </c>
+      <c r="B86" t="n">
+        <v>36</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Feasibility Assessment</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>37</v>
+      </c>
+      <c r="B87" t="n">
+        <v>37</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Prioritization and Decision Making</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>38</v>
+      </c>
+      <c r="B88" t="n">
+        <v>38</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Implementation Planning</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>39</v>
+      </c>
+      <c r="B89" t="n">
+        <v>39</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>40</v>
+      </c>
+      <c r="B90" t="n">
+        <v>40</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Testing and Validation</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>41</v>
+      </c>
+      <c r="B91" t="n">
+        <v>41</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>42</v>
+      </c>
+      <c r="B92" t="n">
+        <v>42</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>43</v>
+      </c>
+      <c r="B93" t="n">
+        <v>43</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Documentation and Knowledge Sharing</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>44</v>
+      </c>
+      <c r="B94" t="n">
+        <v>44</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>45</v>
+      </c>
+      <c r="B95" t="n">
+        <v>45</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Continuous Improvement</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>46</v>
+      </c>
+      <c r="B96" t="n">
+        <v>46</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Problem Solving</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Governance, Risk, and Ethics</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
